--- a/data/availability/projects/nations-of-sky/zomra-east.xlsx
+++ b/data/availability/projects/nations-of-sky/zomra-east.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L10"/>
+  <dimension ref="A1:L9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -558,22 +558,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E2" t="n">
-        <v>60</v>
+        <v>85</v>
       </c>
       <c r="F2" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="G2" t="n">
-        <v>6.6</v>
+        <v>8.9</v>
       </c>
       <c r="H2" t="n">
-        <v>6.6</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -608,22 +608,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D3" t="n">
         <v>2</v>
       </c>
       <c r="E3" t="n">
-        <v>85</v>
+        <v>130</v>
       </c>
       <c r="F3" t="n">
-        <v>90</v>
+        <v>130</v>
       </c>
       <c r="G3" t="n">
-        <v>8.9</v>
+        <v>13.2</v>
       </c>
       <c r="H3" t="n">
-        <v>9.699999999999999</v>
+        <v>14.6</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -654,26 +654,26 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>Duplex</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D4" t="n">
         <v>2</v>
       </c>
       <c r="E4" t="n">
-        <v>130</v>
+        <v>200</v>
       </c>
       <c r="F4" t="n">
-        <v>130</v>
+        <v>220</v>
       </c>
       <c r="G4" t="n">
-        <v>13.2</v>
+        <v>19.1</v>
       </c>
       <c r="H4" t="n">
-        <v>14.6</v>
+        <v>26.5</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -704,7 +704,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Duplex</t>
+          <t>Penthouse</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -714,16 +714,16 @@
         <v>2</v>
       </c>
       <c r="E5" t="n">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="F5" t="n">
-        <v>220</v>
+        <v>250</v>
       </c>
       <c r="G5" t="n">
-        <v>19.1</v>
+        <v>24</v>
       </c>
       <c r="H5" t="n">
-        <v>26.5</v>
+        <v>27.3</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -754,7 +754,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Penthouse</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -764,16 +764,16 @@
         <v>2</v>
       </c>
       <c r="E6" t="n">
-        <v>250</v>
+        <v>210</v>
       </c>
       <c r="F6" t="n">
-        <v>250</v>
+        <v>215</v>
       </c>
       <c r="G6" t="n">
-        <v>24</v>
+        <v>29.2</v>
       </c>
       <c r="H6" t="n">
-        <v>27.3</v>
+        <v>31.8</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -804,26 +804,26 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Townhouse</t>
+          <t>Twin House</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E7" t="n">
-        <v>210</v>
+        <v>270</v>
       </c>
       <c r="F7" t="n">
-        <v>215</v>
+        <v>270</v>
       </c>
       <c r="G7" t="n">
-        <v>29.2</v>
+        <v>41</v>
       </c>
       <c r="H7" t="n">
-        <v>31.8</v>
+        <v>41</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -854,26 +854,26 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Twin House</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C8" t="n">
         <v>4</v>
       </c>
       <c r="D8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E8" t="n">
-        <v>270</v>
+        <v>230</v>
       </c>
       <c r="F8" t="n">
-        <v>270</v>
+        <v>255</v>
       </c>
       <c r="G8" t="n">
         <v>41</v>
       </c>
       <c r="H8" t="n">
-        <v>41</v>
+        <v>55.8</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -908,22 +908,22 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D9" t="n">
         <v>3</v>
       </c>
       <c r="E9" t="n">
-        <v>230</v>
+        <v>315</v>
       </c>
       <c r="F9" t="n">
-        <v>255</v>
+        <v>370</v>
       </c>
       <c r="G9" t="n">
-        <v>41</v>
+        <v>55.8</v>
       </c>
       <c r="H9" t="n">
-        <v>55.8</v>
+        <v>65</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -941,56 +941,6 @@
         </is>
       </c>
       <c r="L9" t="inlineStr">
-        <is>
-          <t>5%+5%+5% over 8-10 yrs</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>zomra-east</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Standalone Villa</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>5</v>
-      </c>
-      <c r="D10" t="n">
-        <v>3</v>
-      </c>
-      <c r="E10" t="n">
-        <v>315</v>
-      </c>
-      <c r="F10" t="n">
-        <v>370</v>
-      </c>
-      <c r="G10" t="n">
-        <v>55.8</v>
-      </c>
-      <c r="H10" t="n">
-        <v>65</v>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>Fully finished</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>Phase 1</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>3 years</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
         <is>
           <t>5%+5%+5% over 8-10 yrs</t>
         </is>
@@ -1007,7 +957,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M19"/>
+  <dimension ref="A1:M18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1090,7 +1040,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ZE-STU</t>
+          <t>ZE-1BR-MIN</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -1099,7 +1049,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -1107,16 +1057,15 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>60</v>
-      </c>
-      <c r="H2" t="inlineStr"/>
+        <v>85</v>
+      </c>
       <c r="I2" t="inlineStr">
         <is>
           <t>Panoramic View</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>6600000</v>
+        <v>8900000</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -1147,7 +1096,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ZE-1BR-MIN</t>
+          <t>ZE-1BR-MAX</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -1164,16 +1113,15 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>85</v>
-      </c>
-      <c r="H3" t="inlineStr"/>
+        <v>90</v>
+      </c>
       <c r="I3" t="inlineStr">
         <is>
           <t>Panoramic View</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>8900000</v>
+        <v>9700000</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -1204,7 +1152,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ZE-1BR-MAX</t>
+          <t>ZE-2BR-MIN</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1213,7 +1161,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1221,16 +1169,15 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>90</v>
-      </c>
-      <c r="H4" t="inlineStr"/>
+        <v>130</v>
+      </c>
       <c r="I4" t="inlineStr">
         <is>
           <t>Panoramic View</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>9700000</v>
+        <v>13200000</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -1261,7 +1208,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ZE-2BR-MIN</t>
+          <t>ZE-2BR-MAX</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1280,14 +1227,13 @@
       <c r="G5" t="n">
         <v>130</v>
       </c>
-      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
           <t>Panoramic View</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>13200000</v>
+        <v>14600000</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -1313,12 +1259,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>Duplex</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ZE-2BR-MAX</t>
+          <t>ZE-SKY-GARDEN-MIN</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1327,7 +1273,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1335,16 +1281,20 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>130</v>
-      </c>
-      <c r="H6" t="inlineStr"/>
+        <v>200</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Garden 40-110 sqm</t>
+        </is>
+      </c>
       <c r="I6" t="inlineStr">
         <is>
           <t>Panoramic View</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>14600000</v>
+        <v>19100000</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -1375,7 +1325,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ZE-SKY-GARDEN-MIN</t>
+          <t>ZE-SKY-GARDEN-MAX</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1392,7 +1342,7 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>200</v>
+        <v>220</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -1405,7 +1355,7 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>19100000</v>
+        <v>26500000</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -1431,12 +1381,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Duplex</t>
+          <t>Penthouse</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ZE-SKY-GARDEN-MAX</t>
+          <t>ZE-SKY-PANO-MIN</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1453,11 +1403,11 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>220</v>
+        <v>250</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Garden 40-110 sqm</t>
+          <t>Roof 50 sqm</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1466,7 +1416,7 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>26500000</v>
+        <v>24000000</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1497,7 +1447,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>ZE-SKY-PANO-MIN</t>
+          <t>ZE-SKY-PANO-MAX</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1527,7 +1477,7 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>24000000</v>
+        <v>27300000</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -1553,12 +1503,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Penthouse</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>ZE-SKY-PANO-MAX</t>
+          <t>ZE-THM</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1575,11 +1525,11 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>250</v>
+        <v>215</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Roof 50 sqm</t>
+          <t>Land 178 sqm</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1588,7 +1538,7 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>27300000</v>
+        <v>29200000</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1619,7 +1569,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>ZE-THM</t>
+          <t>ZE-THC</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1636,11 +1586,11 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Land 178 sqm</t>
+          <t>Land 217 sqm</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1649,7 +1599,7 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>29200000</v>
+        <v>31800000</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1675,12 +1625,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Townhouse</t>
+          <t>Twin House</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>ZE-THC</t>
+          <t>ZE-TW</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1689,7 +1639,7 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1697,11 +1647,11 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>210</v>
+        <v>270</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Land 217 sqm</t>
+          <t>Land 278 sqm</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1710,7 +1660,7 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>31800000</v>
+        <v>41000000</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1736,12 +1686,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Twin House</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>ZE-TW</t>
+          <t>ZE-STD</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1758,11 +1708,11 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>270</v>
+        <v>230</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Land 278 sqm</t>
+          <t>Land 301 sqm</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1802,7 +1752,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>ZE-STD</t>
+          <t>ZE-STC-MIN</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1819,11 +1769,11 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>230</v>
+        <v>255</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Land 301 sqm</t>
+          <t>Land 367 sqm</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1832,7 +1782,7 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>41000000</v>
+        <v>44700000</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -1863,7 +1813,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>ZE-STC-MIN</t>
+          <t>ZE-STC-MAX</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1893,7 +1843,7 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>44700000</v>
+        <v>55800000</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -1924,7 +1874,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>ZE-STC-MAX</t>
+          <t>ZE-STB-MIN</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1933,7 +1883,7 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1941,11 +1891,11 @@
         </is>
       </c>
       <c r="G16" t="n">
-        <v>255</v>
+        <v>315</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Land 367 sqm</t>
+          <t>Land 418 sqm</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1985,7 +1935,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>ZE-STB-MIN</t>
+          <t>ZE-STB-MAX</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2015,7 +1965,7 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>55800000</v>
+        <v>59000000</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -2046,7 +1996,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>ZE-STB-MAX</t>
+          <t>ZE-STA</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2063,11 +2013,11 @@
         </is>
       </c>
       <c r="G18" t="n">
-        <v>315</v>
+        <v>370</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Land 418 sqm</t>
+          <t>Land 720 sqm</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2076,7 +2026,7 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>59000000</v>
+        <v>65000000</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
@@ -2089,67 +2039,6 @@
         </is>
       </c>
       <c r="M18" t="inlineStr">
-        <is>
-          <t>Available</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>zomra-east</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Standalone Villa</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>ZE-STA</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Phase 1</t>
-        </is>
-      </c>
-      <c r="E19" t="n">
-        <v>5</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Fully finished</t>
-        </is>
-      </c>
-      <c r="G19" t="n">
-        <v>370</v>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Land 720 sqm</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>Panoramic View</t>
-        </is>
-      </c>
-      <c r="J19" t="n">
-        <v>65000000</v>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>3 years</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>5%+5%+5% over 8-10 yrs</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
         <is>
           <t>Available</t>
         </is>
